--- a/data/data_preparation/tv/df_relation_matrix.xlsx
+++ b/data/data_preparation/tv/df_relation_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677E62AC-DCEC-C44A-8DC0-8B4E28A8563E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBF8801-F906-5C46-94F7-7917CD10C71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>customer_need</t>
   </si>
@@ -64,9 +64,6 @@
     <t>Peso</t>
   </si>
   <si>
-    <t>Cantidad de parlantes</t>
-  </si>
-  <si>
     <t>Potencia máxima de los parlantes</t>
   </si>
   <si>
@@ -89,12 +86,6 @@
   </si>
   <si>
     <t>Apps integradas_YouTube</t>
-  </si>
-  <si>
-    <t>Apps integradas_Webbrowser</t>
-  </si>
-  <si>
-    <t>Apps integradas_otros</t>
   </si>
   <si>
     <t>imagen</t>
@@ -485,10 +476,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,17 +534,8 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -608,19 +590,10 @@
       <c r="R2">
         <v>0</v>
       </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -641,10 +614,10 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -659,10 +632,10 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -673,214 +646,178 @@
       <c r="R3">
         <v>0</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>9</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>9</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>9</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -913,39 +850,30 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
         <v>1</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
       </c>
       <c r="R7">
         <v>1</v>
       </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -998,19 +926,10 @@
       <c r="R8">
         <v>0</v>
       </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1063,19 +982,10 @@
       <c r="R9">
         <v>0</v>
       </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1128,19 +1038,10 @@
       <c r="R10">
         <v>0</v>
       </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1182,24 +1083,15 @@
         <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
         <v>0</v>
       </c>
     </row>

--- a/data/data_preparation/tv/df_relation_matrix.xlsx
+++ b/data/data_preparation/tv/df_relation_matrix.xlsx
@@ -8,31 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBF8801-F906-5C46-94F7-7917CD10C71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0D7F63-1FB6-AF47-9F09-F86C3FE894BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>customer_need</t>
   </si>
@@ -46,9 +34,6 @@
     <t>Es smart</t>
   </si>
   <si>
-    <t>Con Wi-Fi</t>
-  </si>
-  <si>
     <t>Tipo de pantalla</t>
   </si>
   <si>
@@ -58,9 +43,6 @@
     <t>Tipo de resolución</t>
   </si>
   <si>
-    <t>Resolución máxima</t>
-  </si>
-  <si>
     <t>Peso</t>
   </si>
   <si>
@@ -76,16 +58,25 @@
     <t>Con HDR</t>
   </si>
   <si>
-    <t>Con Bluetooth</t>
-  </si>
-  <si>
-    <t>Con comando de voz integrado</t>
-  </si>
-  <si>
-    <t>Apps integradas_Netflix</t>
-  </si>
-  <si>
-    <t>Apps integradas_YouTube</t>
+    <t>Relación de contraste</t>
+  </si>
+  <si>
+    <t>Brillo</t>
+  </si>
+  <si>
+    <t>Tiempo de respuesta</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>voz</t>
+  </si>
+  <si>
+    <t>conexion</t>
+  </si>
+  <si>
+    <t>diseño</t>
   </si>
   <si>
     <t>imagen</t>
@@ -94,25 +85,10 @@
     <t>sonido</t>
   </si>
   <si>
-    <t>voz</t>
-  </si>
-  <si>
-    <t>usar</t>
-  </si>
-  <si>
-    <t>aplicaciones</t>
-  </si>
-  <si>
-    <t>marca</t>
-  </si>
-  <si>
-    <t>diseño</t>
+    <t>sistema</t>
   </si>
   <si>
     <t>tamaño</t>
-  </si>
-  <si>
-    <t>bluetooth</t>
   </si>
 </sst>
 </file>
@@ -476,10 +452,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,8 +510,11 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -543,7 +522,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -590,10 +569,13 @@
       <c r="R2">
         <v>0</v>
       </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -605,331 +587,349 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>9</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>9</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>9</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>3</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -947,16 +947,16 @@
         <v>3</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -982,10 +982,13 @@
       <c r="R9">
         <v>0</v>
       </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1003,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1038,61 +1041,8 @@
       <c r="R10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>9</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
+      <c r="S10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_preparation/tv/df_relation_matrix.xlsx
+++ b/data/data_preparation/tv/df_relation_matrix.xlsx
@@ -1,26 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0D7F63-1FB6-AF47-9F09-F86C3FE894BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AFF7CC-3464-0C4C-9B6B-92C207B01D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>customer_need</t>
   </si>
@@ -31,52 +43,37 @@
     <t>Marca</t>
   </si>
   <si>
-    <t>Es smart</t>
-  </si>
-  <si>
-    <t>Tipo de pantalla</t>
-  </si>
-  <si>
     <t>Tamaño de la pantalla</t>
   </si>
   <si>
     <t>Tipo de resolución</t>
   </si>
   <si>
+    <t>Brillo</t>
+  </si>
+  <si>
+    <t>Sistema operativo</t>
+  </si>
+  <si>
     <t>Peso</t>
   </si>
   <si>
     <t>Potencia máxima de los parlantes</t>
   </si>
   <si>
-    <t>Sistema operativo</t>
-  </si>
-  <si>
-    <t>Con función screen share</t>
-  </si>
-  <si>
-    <t>Con HDR</t>
-  </si>
-  <si>
     <t>Relación de contraste</t>
   </si>
   <si>
-    <t>Brillo</t>
-  </si>
-  <si>
-    <t>Tiempo de respuesta</t>
-  </si>
-  <si>
     <t>control</t>
   </si>
   <si>
-    <t>voz</t>
+    <t>velocidad</t>
+  </si>
+  <si>
+    <t>diseño</t>
   </si>
   <si>
     <t>conexion</t>
-  </si>
-  <si>
-    <t>diseño</t>
   </si>
   <si>
     <t>imagen</t>
@@ -145,10 +142,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -452,69 +452,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -557,25 +542,10 @@
       <c r="N2">
         <v>0</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -584,16 +554,16 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -602,39 +572,24 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -675,25 +630,10 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -723,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -734,23 +674,8 @@
       <c r="N5">
         <v>0</v>
       </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -770,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -793,144 +718,99 @@
       <c r="N6">
         <v>0</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>1</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
         <v>1</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
+      <c r="N8">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="B9">
         <v>0</v>
       </c>
@@ -938,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -970,25 +850,10 @@
       <c r="N9">
         <v>0</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1027,21 +892,6 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
         <v>1</v>
       </c>
     </row>

--- a/data/data_preparation/tv/df_relation_matrix.xlsx
+++ b/data/data_preparation/tv/df_relation_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AFF7CC-3464-0C4C-9B6B-92C207B01D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1FE73B-E85D-A449-95B1-541A48200FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>customer_need</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Tipo de resolución</t>
   </si>
   <si>
-    <t>Brillo</t>
-  </si>
-  <si>
     <t>Sistema operativo</t>
   </si>
   <si>
@@ -59,9 +56,6 @@
   </si>
   <si>
     <t>Potencia máxima de los parlantes</t>
-  </si>
-  <si>
-    <t>Relación de contraste</t>
   </si>
   <si>
     <t>control</t>
@@ -452,10 +446,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="64" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,17 +483,11 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -536,325 +524,277 @@
       <c r="L2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>1</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
         <v>9</v>
       </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>3</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="B10">
         <v>0</v>
       </c>
@@ -886,12 +826,6 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
         <v>1</v>
       </c>
     </row>

--- a/data/data_preparation/tv/df_relation_matrix.xlsx
+++ b/data/data_preparation/tv/df_relation_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1FE73B-E85D-A449-95B1-541A48200FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F894E0E5-6B29-934E-BDC1-FE689B837EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,16 +43,16 @@
     <t>Marca</t>
   </si>
   <si>
+    <t>Sistema operativo</t>
+  </si>
+  <si>
+    <t>Peso</t>
+  </si>
+  <si>
     <t>Tamaño de la pantalla</t>
   </si>
   <si>
     <t>Tipo de resolución</t>
-  </si>
-  <si>
-    <t>Sistema operativo</t>
-  </si>
-  <si>
-    <t>Peso</t>
   </si>
   <si>
     <t>Potencia máxima de los parlantes</t>
@@ -136,13 +136,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,38 +446,38 @@
   <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -536,16 +533,16 @@
         <v>0</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>9</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -650,13 +647,13 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -764,16 +761,16 @@
         <v>0</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
         <v>9</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>0</v>
